--- a/docs/KSI-Design-Matrix.xlsx
+++ b/docs/KSI-Design-Matrix.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Responsibility Matrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIY" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SVC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CNA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assertion Coverage" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CMT" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCR" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RPL" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CED" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Responsibility Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="IAM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PIY" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SVC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CNA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MLA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Assertion Coverage" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="CMT" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SCR" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="RPL" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="INR" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="CED" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -603,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Shield Standard on the load balancer, plus AWS WAF with managed rule groups and rate limiting</t>
+          <t>Shield Standard on the load balancer, plus AWS WAF with managed rule groups and rate limiting. The offering is served on a subdomain of an owned domain, resolving to the load balancer DNS-only rather than proxied, so no DNS provider sits inside the offering boundary. Public listener certificate is ACM-issued by DNS validation.</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2524,257 +2524,260 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Domains</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>One owned domain, with the project on subdomains rather than the apex. An application subdomain resolving to the load balancer, and a separate subdomain verified for Cloud Identity. The apex is deliberately untouched: verifying it for Cloud Identity would put Google in control of identity for personal correspondence on it.</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Terraform and manual</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>The application certificate for KSI-SVC-ASM and KSI-SVC-SIN, the publication point for KSI-PIY-RVD's security.txt, and the verified domain KSI-IAM-SNU, APM, AAM, ELP and JIT need before Cloud Identity can be the workforce identity provider at all. DNS validation records are created by hand, keeping the DNS provider out of the Terraform execution path and out of KSI-CNA-IBP's third-party register.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>Cost posture</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>Apply and destroy per session. Persisting between sessions: the state backend, evidence storage, the central log store, database snapshots and KMS keys. Snapshots and the log store are excluded from teardown deliberately, because destroying them would leave the recovery and logging clusters with nothing durable to point at.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Standing continuously the stack is roughly 115 to 125 USD per month, with the query and normalization layer adding well under a dollar since Athena is serverless and the transformation Lambda runs per delivery, dominated by the load balancer at 16.20 base, RDS at about 27.71, six interface endpoints at roughly 42 to 49 combined, and WAF at roughly 5 to 8. Security Hub Essentials is priced per resource unit anchored on EC2 instances, with container images at one eighteenth of a unit and IAM principals at one one-hundred-and-twenty-fifth, so an environment with no instances and few images adds only a few dollars.</t>
+          <t>Apply and destroy per session. Persisting between sessions: the state backend, evidence storage, the central log store, database snapshots and KMS keys. Snapshots and the log store are excluded from teardown deliberately, because destroying them would leave the recovery and logging clusters with nothing durable to point at.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
+          <t>The AWS account runs on a paid plan rather than the free plan. That is not only a cost choice: the free plan blocks GuardDuty, Security Hub and Inspector outright and caps RDS backup retention below what the recovery objectives declare, and it expires roughly six months after account creation, after which the account is closed and its resources deleted -- including the object-locked log store. A two-person team running a production offering and pursuing certification would not be on a free plan; being on one was the unrealistic detail. Standing continuously the stack is roughly 115 to 125 USD per month, with the query and normalization layer adding well under a dollar since Athena is serverless and the transformation Lambda runs per delivery, dominated by the load balancer at 16.20 base, RDS at about 27.71, six interface endpoints at roughly 42 to 49 combined, and WAF at roughly 5 to 8. Security Hub Essentials is priced per resource unit anchored on EC2 instances, with container images at one eighteenth of a unit and IAM principals at one one-hundred-and-twenty-fifth, so an environment with no instances and few images adds only a few dollars.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
           <t>Torn down between sessions the residual is under 5 USD per month, mostly KMS keys; RDS backup storage is free up to the size of the instance and log storage is pennies. The exception is AWS Config, which bills per configuration item and therefore charges roughly a dollar per apply-and-destroy cycle, about 10 USD per month at ten sessions; scoping the recorder to needed resource types is the mitigation. A billing alarm at 50 USD is the signal that something was not destroyed.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>Conventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>Determination — In scope: built and proven. In scope, partial: built, but the indicator's literal scope exceeds what is demonstrated, with the gap declared. Deferred: applies, not built, reason and resulting customer risk stated.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Project scope — Non-machine-based information resources (organizational policies, procedures, personnel) are out of scope project-wide. Fabricating them for a synthetic two-person persona would demonstrate nothing. The determination pass still covers all 46 indicators.</t>
+          <t>Determination — In scope: built and proven. In scope, partial: built, but the indicator's literal scope exceeds what is demonstrated, with the gap declared. Deferred: applies, not built, reason and resulting customer risk stated.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Cycle — Required is set by the framework: 3 days for machine-based resources at Class C (VDR-TFR-MVX), 3 months for non-machine (VDR-TFR-NMV). Implemented is what this project actually runs.</t>
+          <t>Project scope — Non-machine-based information resources (organizational policies, procedures, personnel) are out of scope project-wide. Fabricating them for a synthetic two-person persona would demonstrate nothing. The determination pass still covers all 46 indicators.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Evidence — Verification proves the measure exists as described (IVV-CSO-SEI). Validation proves it produces the intended outcome (IVV-CSO-SEE). Both are required per indicator.</t>
+          <t>Cycle — Required is set by the framework: 3 days for machine-based resources at Class C (VDR-TFR-MVX), 3 months for non-machine (VDR-TFR-NMV). Implemented is what this project actually runs.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Assertion decomposition is this project's method, not framework structure. 20x has no objectives layer equivalent to SP 800-171A.</t>
+          <t>Evidence — Verification proves the measure exists as described (IVV-CSO-SEI). Validation proves it produces the intended outcome (IVV-CSO-SEE). Both are required per indicator.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Registers named per indicator (flow control, surface, definition, third-party, availability, protection, integrity, path, retention) are one artifact in implementation: a single resource register generated from the inventory with a column per indicator, so a new resource appears with empty cells that fail their respective checks rather than being silently absent from a dozen separate files.</t>
+          <t>Assertion decomposition is this project's method, not framework structure. 20x has no objectives layer equivalent to SP 800-171A.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>Inventory reconciliation takes three forms. Direct, where an indicator making a coverage claim over resources reconciles against KSI-PIY-GIV. Transitive, where it reconciles against a register that is itself reconciled to the inventory — the source list in KSI-MLA-LET, the third-party register in KSI-CNA-IBP, the objective register in KSI-RPL-RRO. And correctly absent, where the subject is a process rather than a resource population, as in deployment validation, change procedure review and incident response procedure review.</t>
+          <t>Registers named per indicator (flow control, surface, definition, third-party, availability, protection, integrity, path, retention) are one artifact in implementation: a single resource register generated from the inventory with a column per indicator, so a new resource appears with empty cells that fail their respective checks rather than being silently absent from a dozen separate files.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Effectiveness signals are generated by one shared report generator with a section per indicator, not by a scheduled job per indicator. The judgment on top of those signals is a periodic human review, which is organizational activity and is out of scope project-wide on the same basis as personnel and training material. Human decisions taken at a decision point and recorded as structured data — retention choices, accepted risks, benchmark exceptions, dispositions — remain in scope, because the check is that a record exists with the required fields, which is machine-verifiable.</t>
+          <t>Inventory reconciliation takes three forms. Direct, where an indicator making a coverage claim over resources reconciles against KSI-PIY-GIV. Transitive, where it reconciles against a register that is itself reconciled to the inventory — the source list in KSI-MLA-LET, the third-party register in KSI-CNA-IBP, the objective register in KSI-RPL-RRO. And correctly absent, where the subject is a process rather than a resource population, as in deployment validation, change procedure review and incident response procedure review.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
+          <t>Effectiveness signals are generated by one shared report generator with a section per indicator, not by a scheduled job per indicator. The judgment on top of those signals is a periodic human review, which is organizational activity and is out of scope project-wide on the same basis as personnel and training material. Human decisions taken at a decision point and recorded as structured data — retention choices, accepted risks, benchmark exceptions, dispositions — remain in scope, because the check is that a record exists with the required fields, which is machine-verifiable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
           <t>Deliberation lives in DECISIONS.md. This document states what the design is; that one states why, and what else was considered.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+    <row r="93"/>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>Shared components</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="10" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>Build items in the cluster tabs name what an indicator relies on, not what is separately built. The components below are built once and consumed by many indicators; a BUILD row naming one of them is a consumer, not an additional build. The figures are what the determination pass actually produced.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>Consumers</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Built in</t>
         </is>
       </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>Collector framework</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>40 indicators</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>Nine evidence mechanisms: cloud API config read, log query, declared-versus-live comparison, inventory reconciliation, register read, pipeline config read, deliberate test, record store, effective-access analysis.</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>376 evidence rows resolve to these nine. Rows are declarative check definitions on the framework, not separate collectors.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Inventory generator</t>
+          <t>Collector framework</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>27 indicators</t>
+          <t>40 indicators</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Real-time inventory across both clouds from provider asset services.</t>
+          <t>Nine evidence mechanisms: cloud API config read, log query, declared-versus-live comparison, inventory reconciliation, register read, pipeline config read, deliberate test, record store, effective-access analysis.</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Terraform, Python</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Built for KSI-PIY-GIV. 21 indicators reconcile directly, 6 transitively through a register.</t>
+          <t>376 evidence rows resolve to these nine. Rows are declarative check definitions on the framework, not separate collectors.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>Consolidated resource register</t>
+          <t>Inventory generator</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>13 indicators</t>
+          <t>27 indicators</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>One generated register with a column per indicator: positions, exceptions, retention choices, accepted risks, dispositions.</t>
+          <t>Real-time inventory across both clouds from provider asset services.</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>Repo, generated</t>
+          <t>Terraform, Python</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Replaces the dozen per-indicator registers the determinations name individually.</t>
+          <t>Built for KSI-PIY-GIV. 21 indicators reconcile directly, 6 transitively through a register.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>Normalized log corpus</t>
+          <t>Consolidated resource register</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>12 indicators</t>
+          <t>13 indicators</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Both clouds' events mapped to a shared schema, partitioned Parquet in the object-locked store.</t>
+          <t>One generated register with a column per indicator: positions, exceptions, retention choices, accepted risks, dispositions.</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Terraform, Python</t>
+          <t>Repo, generated</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>Built for KSI-MLA-OSM. Everything reading logs reads this.</t>
+          <t>Replaces the dozen per-indicator registers the determinations name individually.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>Query layer</t>
+          <t>Normalized log corpus</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -2784,34 +2787,34 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Serverless query engine over the corpus with partition projection and per-query scan limits.</t>
+          <t>Both clouds' events mapped to a shared schema, partitioned Parquet in the object-locked store.</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Terraform</t>
+          <t>Terraform, Python</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>50 log-query evidence rows are SQL files against this, not separate engines.</t>
+          <t>Built for KSI-MLA-OSM. Everything reading logs reads this.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>Detection path</t>
+          <t>Query layer</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>9 indicators</t>
+          <t>12 indicators</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Findings and alerts routed to the responder and recorded.</t>
+          <t>Serverless query engine over the corpus with partition projection and per-query scan limits.</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -2821,14 +2824,14 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>Built for KSI-IAM-SUS. Everything that escalates escalates here.</t>
+          <t>50 log-query evidence rows are SQL files against this, not separate engines.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>Vulnerability scanner</t>
+          <t>Detection path</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
@@ -2838,61 +2841,61 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Image and dependency scanning with findings into the response pipeline.</t>
+          <t>Findings and alerts routed to the responder and recorded.</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Terraform, CI</t>
+          <t>Terraform</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>One scanner. Cited by evaluation, supply chain, attack surface and SDLC indicators.</t>
+          <t>Built for KSI-IAM-SUS. Everything that escalates escalates here.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>Standing-query self-test harness</t>
+          <t>Vulnerability scanner</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>34 indicators</t>
+          <t>9 indicators</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Each zero-results query registers a seed action; the harness seeds, confirms the query stops returning zero, and reverts.</t>
+          <t>Image and dependency scanning with findings into the response pipeline.</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Python, CI</t>
+          <t>Terraform, CI</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>65 standing queries. Without this a query watching the wrong thing returns zero forever and looks correct.</t>
+          <t>One scanner. Cited by evaluation, supply chain, attack surface and SDLC indicators.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Deliberate test harness</t>
+          <t>Standing-query self-test harness</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>12 indicators</t>
+          <t>34 indicators</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Break a real thing, confirm the collector fails, revert, confirm it passes.</t>
+          <t>Each zero-results query registers a seed action; the harness seeds, confirms the query stops returning zero, and reverts.</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -2902,86 +2905,113 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>23 scenarios. Slow, unshareable, and the only evidence the collectors detect anything.</t>
+          <t>65 standing queries. Without this a query watching the wrong thing returns zero forever and looks correct.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>Signal report generator</t>
+          <t>Deliberate test harness</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>7 indicators</t>
+          <t>12 indicators</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>One report with a section per indicator aggregating its effectiveness signals.</t>
+          <t>Break a real thing, confirm the collector fails, revert, confirm it passes.</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Terraform, Python</t>
+          <t>Python, CI</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Replaces seven per-indicator scheduled review jobs.</t>
+          <t>23 scenarios. Slow, unshareable, and the only evidence the collectors detect anything.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>SDR emitter</t>
+          <t>Signal report generator</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>40 indicators</t>
+          <t>7 indicators</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Security Decision Record output in human-readable and JSON form against SDR-CSO-FRR and SDR-CSX-KSI.</t>
+          <t>One report with a section per indicator aggregating its effectiveness signals.</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Terraform, Python</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>One emitter reading determinations and evidence; not per-indicator.</t>
+          <t>Replaces seven per-indicator scheduled review jobs.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
+          <t>SDR emitter</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>40 indicators</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Security Decision Record output in human-readable and JSON form against SDR-CSO-FRR and SDR-CSX-KSI.</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>One emitter reading determinations and evidence; not per-indicator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>Terraform for both clouds, the pipeline, and the workflows for elevation, response and token rotation.</t>
         </is>
       </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>Terraform</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E108" s="6" t="inlineStr">
         <is>
           <t>The substrate everything else runs against.</t>
         </is>
@@ -3118,7 +3148,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Provider security bulletins and ecosystem advisory feeds ingested into the central store and normalized.</t>
+          <t>Provider security bulletins and ecosystem advisory feeds ingested into the central store and normalized. Named sources: OSV as primary and the GitHub Advisory Database as second for ecosystem advisories, both covering the language ecosystems in the pinned manifests; vendor security bulletins for provider-side advisories.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -3168,7 +3198,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Service change and deprecation notifications ingested, since a changed default is a vulnerability under the definition and produces no advisory.</t>
+          <t>Service change and deprecation notifications ingested, since a changed default is a vulnerability under the definition and produces no advisory. Source not yet fixed: the provider health API is the obvious one and programmatic access has historically required a paid support plan. To be verified against current documentation and decided as a cost question rather than assumed in either direction.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -3604,7 +3634,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Every component version compared against its published support window, with findings kept distinct from vulnerability findings because the remediation differs.</t>
+          <t>Every component version compared against its published support window, with findings kept distinct from vulnerability findings because the remediation differs -- a patched component can still be unsupported. Support windows sourced from endoflife.date.</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -12795,7 +12825,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Served at the well-known path with contact, policy link, preferred languages and a maintained expiry.</t>
+          <t>Served at the well-known path with contact, policy link, preferred languages and a maintained expiry. Published by the load balancer as a fixed response rather than by the application, so the disclosure channel survives an application outage and no unauthenticated public path enters request handling. Expiry carried by a rotating timestamp on a ninety-day period, not the apply timestamp -- a value that re-evaluated every plan would leave KSI-SVC-ACM's drift signal permanently positive. Policy line omitted entirely when no URL is published.</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -15505,7 +15535,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>ACM-issued certificates with automatic renewal for the load balancer and task-side TLS.</t>
+          <t>Split by hop, because the two halves resolve differently. Load balancer listener: ACM-issued via DNS validation on the offering's domain, automatic renewal, no cost. Task-side: self-signed, because the load balancer does not validate target certificates and AWS documents VPC target traffic as authenticated at the packet level -- a trusted chain would be verified by nothing in the path. Authenticity on that hop is established by platform identity under KSI-SVC-VCM. Validation records created by hand; the certificate is issued in the bootstrap root so teardown does not destroy it.</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -16045,7 +16075,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Images signed at build; signatures stored alongside them in the registry.</t>
+          <t>Images signed at build; signatures stored alongside them in the registry as OCI artifacts. Keyless signing with the pipeline's federated identity rather than a managed signing service: no signing key exists to store, protect or rotate, holding the KSI-IAM-SNU position rather than reopening it. The signing identity is the workflow, repository and commit, recorded in a public transparency log.</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -16095,7 +16125,7 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>Signature verified before deployment. Failure blocks rather than warns.</t>
+          <t>Signature verified before deployment, with identity conditions on the signer rather than merely on the presence of a signature. Failure blocks rather than warns. Sequence-enforced rather than admission-enforced: the container service provides no admission control for image signatures, so the bypass is closed by IAM instead -- only the pipeline principal may push images or update services. Declared, not implied.</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -18474,7 +18504,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Versioned list of resources permitted inbound from the internet. Currently the load balancer only.</t>
+          <t>Versioned list of resources permitted inbound from the internet. Currently the load balancer only. The application domain resolves to it directly, DNS-only rather than proxied: proxied mode would place the DNS provider inside the offering boundary, terminate TLS there, and add it to KSI-CNA-IBP's third-party register, for capability WAF and Shield Standard already supply.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -29281,7 +29311,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Declared-state apply permitted only to the pipeline principal, enforced by role rather than by convention.</t>
+          <t>Declared-state apply permitted only to the pipeline principal, enforced by role rather than by convention. Currently held open by a dated entry in the exception register: a human identity retains apply because the elevation path is KSI-IAM-JIT's and the dependency is circular -- the pipeline deploys JIT. The exception carries a named closing condition rather than being undated.</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -29768,7 +29798,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Commit and pull request events delivered to the central store and normalized with the rest.</t>
+          <t>Commit and pull request events delivered to the central store and normalized with the rest. Emitted by the pipeline to the event bus using the federated identity it already holds, rather than a webhook into a public endpoint -- no new ingress and no shared secret to rotate. Captures events that trigger a workflow run rather than every repository event; branch protection routes changes through pull requests, so coverage is good rather than total.</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
